--- a/data/trans_bre/P23_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,08; -19,17</t>
+          <t>-26,5; -19,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,92; -15,34</t>
+          <t>-23,0; -15,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,77; -11,96</t>
+          <t>-20,71; -12,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-68,71; -56,59</t>
+          <t>-68,69; -56,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,87; -48,25</t>
+          <t>-63,0; -49,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,18; -44,22</t>
+          <t>-63,15; -44,04</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,6; -10,36</t>
+          <t>-17,05; -10,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,3; -3,82</t>
+          <t>-10,94; -4,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,9; -2,93</t>
+          <t>-9,28; -2,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,02; -22,19</t>
+          <t>-34,15; -22,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,98; -9,36</t>
+          <t>-24,24; -9,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,77; -7,98</t>
+          <t>-22,49; -7,07</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 0,27</t>
+          <t>-11,4; -0,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 3,61</t>
+          <t>-9,44; 4,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 1,99</t>
+          <t>-8,19; 2,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 0,58</t>
+          <t>-30,49; 0,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 12,34</t>
+          <t>-25,71; 14,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 8,55</t>
+          <t>-29,49; 10,79</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,98; -14,32</t>
+          <t>-19,08; -14,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,19; -9,56</t>
+          <t>-14,52; -9,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -6,64</t>
+          <t>-10,96; -6,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -34,82</t>
+          <t>-43,64; -35,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,78; -24,79</t>
+          <t>-35,65; -25,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,52; -19,4</t>
+          <t>-30,27; -19,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P23_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P23_R-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,5; -19,68</t>
+          <t>-26,42; -19,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,0; -15,99</t>
+          <t>-23,12; -15,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,71; -12,38</t>
+          <t>-19,82; -12,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-68,69; -56,92</t>
+          <t>-68,5; -55,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,0; -49,59</t>
+          <t>-62,99; -49,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,15; -44,04</t>
+          <t>-61,97; -44,43</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,05; -10,27</t>
+          <t>-17,39; -10,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,94; -4,16</t>
+          <t>-10,32; -3,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,28; -2,7</t>
+          <t>-9,15; -3,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,15; -22,14</t>
+          <t>-34,77; -22,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,24; -9,7</t>
+          <t>-23,34; -9,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -7,07</t>
+          <t>-22,29; -8,3</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,4; -0,01</t>
+          <t>-11,51; 0,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 4,21</t>
+          <t>-9,86; 3,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 2,4</t>
+          <t>-8,34; 2,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 0,21</t>
+          <t>-30,63; 0,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-25,71; 14,33</t>
+          <t>-26,22; 10,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 10,79</t>
+          <t>-30,06; 11,48</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -14,65</t>
+          <t>-18,96; -14,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -9,76</t>
+          <t>-14,38; -9,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,96; -6,56</t>
+          <t>-11,25; -6,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,64; -35,66</t>
+          <t>-43,67; -35,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,65; -25,57</t>
+          <t>-35,23; -24,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,27; -19,26</t>
+          <t>-30,88; -19,18</t>
         </is>
       </c>
     </row>
